--- a/Team-Data/2013-14/3-13-2013-14.xlsx
+++ b/Team-Data/2013-14/3-13-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,37 +728,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F2" t="n">
         <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>0.444</v>
+        <v>0.435</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J2" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K2" t="n">
         <v>0.459</v>
       </c>
       <c r="L2" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="M2" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.378</v>
+        <v>0.376</v>
       </c>
       <c r="O2" t="n">
         <v>16.8</v>
@@ -700,13 +767,13 @@
         <v>21.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R2" t="n">
         <v>8.9</v>
       </c>
       <c r="S2" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T2" t="n">
         <v>40</v>
@@ -718,7 +785,7 @@
         <v>15.3</v>
       </c>
       <c r="W2" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X2" t="n">
         <v>4.2</v>
@@ -736,19 +803,19 @@
         <v>101.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF2" t="n">
         <v>18</v>
       </c>
       <c r="AG2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH2" t="n">
         <v>10</v>
@@ -757,7 +824,7 @@
         <v>18</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK2" t="n">
         <v>9</v>
@@ -769,7 +836,7 @@
         <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
         <v>21</v>
@@ -793,16 +860,16 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
         <v>24</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
         <v>4</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -927,13 +994,13 @@
         <v>25</v>
       </c>
       <c r="AF3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI3" t="n">
         <v>25</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1182,7 @@
         <v>14</v>
       </c>
       <c r="AH4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -1389,88 +1456,88 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
         <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>0.554</v>
+        <v>0.547</v>
       </c>
       <c r="H6" t="n">
         <v>48.7</v>
       </c>
       <c r="I6" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="J6" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
       <c r="L6" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.347</v>
+        <v>0.342</v>
       </c>
       <c r="O6" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R6" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S6" t="n">
         <v>33</v>
       </c>
       <c r="T6" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="U6" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="V6" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="W6" t="n">
         <v>7.2</v>
       </c>
       <c r="X6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y6" t="n">
         <v>6.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AA6" t="n">
         <v>21.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF6" t="n">
         <v>13</v>
@@ -1488,10 +1555,10 @@
         <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM6" t="n">
         <v>27</v>
@@ -1542,7 +1609,7 @@
         <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1728,7 @@
         <v>22</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
         <v>23</v>
@@ -1679,7 +1746,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO7" t="n">
         <v>16</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1934,7 @@
         <v>18</v>
       </c>
       <c r="AP8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
@@ -2022,10 +2089,10 @@
         <v>19</v>
       </c>
       <c r="AG9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
         <v>12</v>
@@ -2043,7 +2110,7 @@
         <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
@@ -2061,7 +2128,7 @@
         <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
         <v>12</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2322,7 @@
         <v>5</v>
       </c>
       <c r="AX10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY10" t="n">
         <v>17</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -2401,13 +2468,13 @@
         <v>10</v>
       </c>
       <c r="AL11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM11" t="n">
         <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO11" t="n">
         <v>23</v>
@@ -2419,13 +2486,13 @@
         <v>23</v>
       </c>
       <c r="AR11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT11" t="n">
         <v>3</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>4</v>
       </c>
       <c r="AU11" t="n">
         <v>8</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -2481,70 +2548,70 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" t="n">
         <v>44</v>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>0.677</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37.6</v>
+        <v>37.8</v>
       </c>
       <c r="J12" t="n">
         <v>79.59999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.473</v>
+        <v>0.475</v>
       </c>
       <c r="L12" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>25.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0.351</v>
+        <v>0.354</v>
       </c>
       <c r="O12" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="P12" t="n">
         <v>31.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.698</v>
+        <v>0.697</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="T12" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="U12" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V12" t="n">
         <v>16.4</v>
       </c>
       <c r="W12" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X12" t="n">
         <v>5.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
         <v>20.2</v>
@@ -2553,25 +2620,25 @@
         <v>24.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.2</v>
+        <v>106.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
       </c>
       <c r="AF12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG12" t="n">
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI12" t="n">
         <v>17</v>
@@ -2580,16 +2647,16 @@
         <v>28</v>
       </c>
       <c r="AK12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM12" t="n">
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2601,13 +2668,13 @@
         <v>29</v>
       </c>
       <c r="AR12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS12" t="n">
         <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU12" t="n">
         <v>22</v>
@@ -2616,13 +2683,13 @@
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX12" t="n">
         <v>6</v>
       </c>
       <c r="AY12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ12" t="n">
         <v>12</v>
@@ -2631,7 +2698,7 @@
         <v>1</v>
       </c>
       <c r="BB12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -2741,16 +2808,16 @@
         <v>6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
         <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="n">
         <v>19</v>
@@ -2771,7 +2838,7 @@
         <v>24</v>
       </c>
       <c r="AN13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
@@ -2795,7 +2862,7 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2980,7 +3047,7 @@
         <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX14" t="n">
         <v>16</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E15" t="n">
         <v>22</v>
       </c>
       <c r="F15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G15" t="n">
-        <v>0.338</v>
+        <v>0.344</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3045,7 +3112,7 @@
         <v>37.8</v>
       </c>
       <c r="J15" t="n">
-        <v>84.3</v>
+        <v>84.2</v>
       </c>
       <c r="K15" t="n">
         <v>0.449</v>
@@ -3057,7 +3124,7 @@
         <v>24.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.385</v>
+        <v>0.383</v>
       </c>
       <c r="O15" t="n">
         <v>16.9</v>
@@ -3066,16 +3133,16 @@
         <v>22.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.749</v>
+        <v>0.752</v>
       </c>
       <c r="R15" t="n">
         <v>9.1</v>
       </c>
       <c r="S15" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T15" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U15" t="n">
         <v>23.8</v>
@@ -3090,28 +3157,28 @@
         <v>5.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z15" t="n">
         <v>20.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB15" t="n">
         <v>102</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.2</v>
+        <v>-5.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
       </c>
       <c r="AF15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG15" t="n">
         <v>25</v>
@@ -3126,7 +3193,7 @@
         <v>9</v>
       </c>
       <c r="AK15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL15" t="n">
         <v>2</v>
@@ -3144,7 +3211,7 @@
         <v>19</v>
       </c>
       <c r="AQ15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR15" t="n">
         <v>25</v>
@@ -3168,19 +3235,19 @@
         <v>3</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ15" t="n">
         <v>10</v>
       </c>
       <c r="BA15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BB15" t="n">
         <v>12</v>
       </c>
       <c r="BC15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>1.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>10</v>
@@ -3305,7 +3372,7 @@
         <v>16</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK16" t="n">
         <v>7</v>
@@ -3326,7 +3393,7 @@
         <v>29</v>
       </c>
       <c r="AQ16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
@@ -3338,7 +3405,7 @@
         <v>19</v>
       </c>
       <c r="AU16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV16" t="n">
         <v>4</v>
@@ -3362,7 +3429,7 @@
         <v>25</v>
       </c>
       <c r="BC16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E18" t="n">
         <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2</v>
+        <v>0.203</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
@@ -3591,49 +3658,49 @@
         <v>35.6</v>
       </c>
       <c r="J18" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K18" t="n">
         <v>0.431</v>
       </c>
       <c r="L18" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M18" t="n">
         <v>20.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.354</v>
+        <v>0.356</v>
       </c>
       <c r="O18" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P18" t="n">
         <v>21.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.758</v>
+        <v>0.757</v>
       </c>
       <c r="R18" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S18" t="n">
         <v>29.6</v>
       </c>
       <c r="T18" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U18" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V18" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W18" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X18" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y18" t="n">
         <v>5.2</v>
@@ -3645,13 +3712,13 @@
         <v>20.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="AC18" t="n">
         <v>-8</v>
       </c>
       <c r="AD18" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,7 +3730,7 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI18" t="n">
         <v>28</v>
@@ -3672,7 +3739,7 @@
         <v>16</v>
       </c>
       <c r="AK18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL18" t="n">
         <v>18</v>
@@ -3681,13 +3748,13 @@
         <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO18" t="n">
         <v>25</v>
       </c>
       <c r="AP18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ18" t="n">
         <v>16</v>
@@ -3711,7 +3778,7 @@
         <v>28</v>
       </c>
       <c r="AX18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY18" t="n">
         <v>19</v>
@@ -3720,7 +3787,7 @@
         <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3948,7 @@
         <v>12</v>
       </c>
       <c r="AT19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="n">
         <v>6</v>
@@ -3905,7 +3972,7 @@
         <v>3</v>
       </c>
       <c r="BB19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC19" t="n">
         <v>9</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4039,7 +4106,7 @@
         <v>11</v>
       </c>
       <c r="AL20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM20" t="n">
         <v>29</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR21" t="n">
         <v>19</v>
@@ -4266,7 +4333,7 @@
         <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB21" t="n">
         <v>20</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -4301,58 +4368,58 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E22" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F22" t="n">
         <v>17</v>
       </c>
       <c r="G22" t="n">
-        <v>0.738</v>
+        <v>0.734</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
       </c>
       <c r="I22" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="J22" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="K22" t="n">
         <v>0.475</v>
       </c>
       <c r="L22" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M22" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.361</v>
+        <v>0.359</v>
       </c>
       <c r="O22" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="P22" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.806</v>
+        <v>0.803</v>
       </c>
       <c r="R22" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S22" t="n">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="T22" t="n">
-        <v>45.5</v>
+        <v>45.2</v>
       </c>
       <c r="U22" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V22" t="n">
         <v>15.8</v>
@@ -4361,28 +4428,28 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Y22" t="n">
         <v>3.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA22" t="n">
         <v>20.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>106.1</v>
+        <v>105.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
         <v>2</v>
@@ -4391,16 +4458,16 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI22" t="n">
         <v>4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL22" t="n">
         <v>16</v>
@@ -4409,13 +4476,13 @@
         <v>16</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
@@ -4424,13 +4491,13 @@
         <v>17</v>
       </c>
       <c r="AS22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AU22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV22" t="n">
         <v>28</v>
@@ -4445,7 +4512,7 @@
         <v>3</v>
       </c>
       <c r="AZ22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA22" t="n">
         <v>18</v>
@@ -4454,7 +4521,7 @@
         <v>5</v>
       </c>
       <c r="BC22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-11.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4755,7 +4822,7 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI24" t="n">
         <v>13</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE25" t="n">
         <v>11</v>
@@ -4961,7 +5028,7 @@
         <v>9</v>
       </c>
       <c r="AP25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ25" t="n">
         <v>17</v>
@@ -4979,7 +5046,7 @@
         <v>29</v>
       </c>
       <c r="AV25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW25" t="n">
         <v>9</v>
@@ -4991,7 +5058,7 @@
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA25" t="n">
         <v>8</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -5119,7 +5186,7 @@
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI26" t="n">
         <v>3</v>
@@ -5128,7 +5195,7 @@
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
         <v>4</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -5301,13 +5368,13 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI27" t="n">
         <v>21</v>
       </c>
       <c r="AJ27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK27" t="n">
         <v>18</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>6.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5528,7 +5595,7 @@
         <v>15</v>
       </c>
       <c r="AW28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX28" t="n">
         <v>12</v>
@@ -5546,7 +5613,7 @@
         <v>7</v>
       </c>
       <c r="BC28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -5841,13 +5908,13 @@
         <v>25</v>
       </c>
       <c r="AF30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI30" t="n">
         <v>26</v>
@@ -5865,7 +5932,7 @@
         <v>23</v>
       </c>
       <c r="AN30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO30" t="n">
         <v>22</v>
@@ -5904,13 +5971,13 @@
         <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB30" t="n">
         <v>28</v>
       </c>
       <c r="BC30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6086,7 +6153,7 @@
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB31" t="n">
         <v>16</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-13-2013-14</t>
+          <t>2014-03-13</t>
         </is>
       </c>
     </row>
